--- a/data/trans_orig/IP07_A12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A12_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3342</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2808</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8541</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15299</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,47%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,54%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4073</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8453</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,39%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37217</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5881</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2519</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10940</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4381</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1577</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8382</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56565</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49073</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>62572</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>47565</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41721</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52128</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>80,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>60121</t>
+          <t>47150</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45867</t>
+          <t>40693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68965</t>
+          <t>51876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>107685</t>
+          <t>103714</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91922</t>
+          <t>93822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116693</t>
+          <t>111988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74498</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>74498</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>74498</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58726</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58726</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>58726</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>141640</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141640</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141640</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>913</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>983</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5490</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5862</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9005</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4792</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15779</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10184</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5898</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15612</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40005</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33354</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>45382</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>37752</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>31874</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42992</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>69,26%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40027</t>
+          <t>39369</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>32960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45558</t>
+          <t>44974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>77779</t>
+          <t>79374</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68879</t>
+          <t>69147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85944</t>
+          <t>87218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54092</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54092</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54092</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54511</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54511</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>54511</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54531</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54531</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54531</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>109041</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>109041</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>109041</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4007</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4134</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3801</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>5284</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,98%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3278</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7890</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4333</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8872</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>26,24%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5861</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2899</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>10498</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>25131</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19584</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>29117</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>74,33%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>57,92%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>24085</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>19233</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>27290</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>78,39%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>62,6%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>21364</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>50218</t>
+          <t>51444</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44385</t>
+          <t>43916</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55593</t>
+          <t>57242</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4348</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10779</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5730</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4493</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1539</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>11248</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13189</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4742</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4706</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4200</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>10390</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>6085</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>12108</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>33637</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>23116</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>47139</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>40,29%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>16642</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>7730</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>24788</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>35543</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51511</t>
+          <t>23875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>52185</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33337</t>
+          <t>38477</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70637</t>
+          <t>67808</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>73854</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>59858</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>84854</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>63,12%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>51,16%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>72,52%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>92041</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>80283</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>106295</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>78,26%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>68,27%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>75947</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60655</t>
+          <t>60303</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87165</t>
+          <t>75387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>167988</t>
+          <t>141301</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>148327</t>
+          <t>124352</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>191302</t>
+          <t>155145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>117001</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>117001</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>117001</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>117605</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>117605</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>117605</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>121298</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>121298</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>121298</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>238903</t>
+          <t>211203</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>238903</t>
+          <t>211203</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>238903</t>
+          <t>211203</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>4793</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1797</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>10211</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>349</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>12376</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>4546</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>9221</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10884</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>18235</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>13193</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>7876</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>23965</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>21,05%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>38,24%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>24042</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>36041</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>68802</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>59907</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>76349</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>78,95%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>68,74%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>87,61%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>38321</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>30224</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>44931</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>71,69%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>74190</t>
+          <t>41576</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>65468</t>
+          <t>34335</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>81073</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>112510</t>
+          <t>110378</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>100432</t>
+          <t>99177</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>123991</t>
+          <t>120221</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>87147</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>87147</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>87147</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>92167</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>92167</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>92167</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>154843</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>154843</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>154843</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>5804</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>3475</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>7913</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1492</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>4737</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>3308</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>559</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>12064</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>19644</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>25,85%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>15,86%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>42,09%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>3639</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>12580</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>31,0%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19856</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13406</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>26843</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>25389</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>32149</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>33426</t>
+          <t>29217</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>26955</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>34636</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>60269</t>
+          <t>61905</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>51750</t>
+          <t>52990</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>67516</t>
+          <t>69662</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>46672</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>46672</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>46672</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>40577</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>40577</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>40577</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>90776</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>90776</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>90776</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11270</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>6439</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>19304</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>14977</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>9240</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>23508</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>24228</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>35887</t>
+          <t>37787</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>5465</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>11446</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>13664</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>21177</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>23637</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>15881</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>34201</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>18326</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>11739</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>26322</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>48398</t>
+          <t>28150</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>66906</t>
+          <t>55724</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>75805</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>60172</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>94456</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>22,86%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>57581</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>43781</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>73902</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>20,26%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>78175</t>
+          <t>57164</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>62696</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>100179</t>
+          <t>73156</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>135756</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>111826</t>
+          <t>112169</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>161645</t>
+          <t>154048</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>297044</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>275919</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>314432</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>71,88%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>66,77%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>76,09%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>266607</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>247851</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>288458</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>73,08%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>67,94%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>79,07%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>309844</t>
+          <t>251071</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>287501</t>
+          <t>234535</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>329701</t>
+          <t>266348</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>576450</t>
+          <t>548115</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>547418</t>
+          <t>522596</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>609343</t>
+          <t>570887</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>74,72%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>413221</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>413221</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>413221</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>469</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>364819</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>364819</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>364819</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>432567</t>
+          <t>350838</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>432567</t>
+          <t>350838</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>432567</t>
+          <t>350838</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>797386</t>
+          <t>764059</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>797386</t>
+          <t>764059</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>797386</t>
+          <t>764059</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
